--- a/outputs/kaggle_sam_output_points.xlsx
+++ b/outputs/kaggle_sam_output_points.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>image_name</t>
+          <t>image</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -446,52 +446,52 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>class_name</t>
+          <t>raw_label</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>class_id</t>
+          <t>kicad_class</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>kicad_footprint</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>box_x1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>box_y1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>box_x2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>box_y2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>num_polygon_points</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>polygon_points_json</t>
-        </is>
-      </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>polygon_points_compact</t>
+          <t>polygon_points</t>
         </is>
       </c>
     </row>
@@ -514,35 +514,37 @@
           <t>Resistor</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Resistor_SMD</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>828</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>842</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>911</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>910</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>0.919</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>17</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>[[847.0, 855.0], [832.0, 876.0], [831.0, 884.0], [841.0, 888.0], [852.0, 895.0], [863.0, 899.0], [872.0, 899.0], [878.0, 901.0], [885.0, 907.0], [892.0, 908.0], [902.0, 886.0], [902.0, 881.0], [894.0, 866.0], [886.0, 858.0], [878.0, 854.0], [858.0, 856.0], [852.0, 854.0]]</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>(847.0,855.0); (832.0,876.0); (831.0,884.0); (841.0,888.0); (852.0,895.0); (863.0,899.0); (872.0,899.0); (878.0,901.0); (885.0,907.0); (892.0,908.0); (902.0,886.0); (902.0,881.0); (894.0,866.0); (886.0,858.0); (878.0,854.0); (858.0,856.0); (852.0,854.0)</t>
         </is>
       </c>
     </row>
@@ -565,35 +567,37 @@
           <t>MOSFET</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD:SOT-23</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>490</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>712</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>636</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>845</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>0.946</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>22</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>[[550.0, 724.0], [540.0, 729.0], [528.0, 744.0], [515.0, 766.0], [513.0, 775.0], [551.0, 803.0], [560.0, 806.0], [560.0, 815.0], [564.0, 818.0], [570.0, 816.0], [574.0, 820.0], [571.0, 827.0], [578.0, 828.0], [592.0, 823.0], [605.0, 808.0], [621.0, 780.0], [621.0, 772.0], [598.0, 751.0], [591.0, 750.0], [578.0, 737.0], [572.0, 735.0], [563.0, 725.0]]</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>(550.0,724.0); (540.0,729.0); (528.0,744.0); (515.0,766.0); (513.0,775.0); (551.0,803.0); (560.0,806.0); (560.0,815.0); (564.0,818.0); (570.0,816.0); (574.0,820.0); (571.0,827.0); (578.0,828.0); (592.0,823.0); (605.0,808.0); (621.0,780.0); (621.0,772.0); (598.0,751.0); (591.0,750.0); (578.0,737.0); (572.0,735.0); (563.0,725.0)</t>
         </is>
       </c>
     </row>
@@ -616,35 +620,37 @@
           <t>Transformer</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>7</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Transformer_SMD</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Transformer_SMD:Transformer_Wuerth_WE-PoE_EP13</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>644</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>658</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>864</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>878</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>0.827</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>26</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>[[809.0, 692.0], [796.0, 696.0], [788.0, 704.0], [765.0, 689.0], [746.0, 697.0], [728.0, 715.0], [730.0, 731.0], [702.0, 743.0], [698.0, 759.0], [668.0, 785.0], [665.0, 794.0], [723.0, 838.0], [732.0, 833.0], [735.0, 836.0], [730.0, 841.0], [737.0, 846.0], [744.0, 842.0], [758.0, 849.0], [766.0, 844.0], [765.0, 838.0], [751.0, 835.0], [764.0, 807.0], [801.0, 766.0], [801.0, 759.0], [827.0, 710.0], [823.0, 701.0]]</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>(809.0,692.0); (796.0,696.0); (788.0,704.0); (765.0,689.0); (746.0,697.0); (728.0,715.0); (730.0,731.0); (702.0,743.0); (698.0,759.0); (668.0,785.0); (665.0,794.0); (723.0,838.0); (732.0,833.0); (735.0,836.0); (730.0,841.0); (737.0,846.0); (744.0,842.0); (758.0,849.0); (766.0,844.0); (765.0,838.0); (751.0,835.0); (764.0,807.0); (801.0,766.0); (801.0,759.0); (827.0,710.0); (823.0,701.0)</t>
         </is>
       </c>
     </row>
@@ -667,35 +673,37 @@
           <t>Cap3</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>598</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>576</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>772</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>754</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>0.975</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>16</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>[[733.0, 614.0], [709.0, 601.0], [684.0, 601.0], [669.0, 609.0], [640.0, 640.0], [619.0, 650.0], [612.0, 660.0], [608.0, 683.0], [611.0, 697.0], [623.0, 716.0], [645.0, 728.0], [667.0, 728.0], [731.0, 694.0], [741.0, 684.0], [749.0, 660.0], [746.0, 633.0]]</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>(733.0,614.0); (709.0,601.0); (684.0,601.0); (669.0,609.0); (640.0,640.0); (619.0,650.0); (612.0,660.0); (608.0,683.0); (611.0,697.0); (623.0,716.0); (645.0,728.0); (667.0,728.0); (731.0,694.0); (741.0,684.0); (749.0,660.0); (746.0,633.0)</t>
         </is>
       </c>
     </row>
@@ -718,35 +726,37 @@
           <t>Cap4</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>504</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>518</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>672</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>700</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>0.979</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>17</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>[[634.0, 556.0], [609.0, 544.0], [583.0, 545.0], [563.0, 556.0], [544.0, 579.0], [528.0, 590.0], [520.0, 648.0], [532.0, 664.0], [544.0, 670.0], [578.0, 668.0], [592.0, 662.0], [603.0, 652.0], [617.0, 649.0], [636.0, 639.0], [649.0, 618.0], [651.0, 586.0], [648.0, 575.0]]</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>(634.0,556.0); (609.0,544.0); (583.0,545.0); (563.0,556.0); (544.0,579.0); (528.0,590.0); (520.0,648.0); (532.0,664.0); (544.0,670.0); (578.0,668.0); (592.0,662.0); (603.0,652.0); (617.0,649.0); (636.0,639.0); (649.0,618.0); (651.0,586.0); (648.0,575.0)</t>
         </is>
       </c>
     </row>
@@ -769,35 +779,37 @@
           <t>Cap2</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>334</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>1102</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>430</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>1199</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>0.922</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>16</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>[[380.0, 1111.0], [369.0, 1115.0], [366.0, 1124.0], [357.0, 1134.0], [352.0, 1148.0], [352.0, 1159.0], [355.0, 1167.0], [365.0, 1178.0], [378.0, 1185.0], [388.0, 1187.0], [402.0, 1182.0], [416.0, 1169.0], [420.0, 1160.0], [420.0, 1144.0], [416.0, 1132.0], [402.0, 1118.0]]</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>(380.0,1111.0); (369.0,1115.0); (366.0,1124.0); (357.0,1134.0); (352.0,1148.0); (352.0,1159.0); (355.0,1167.0); (365.0,1178.0); (378.0,1185.0); (388.0,1187.0); (402.0,1182.0); (416.0,1169.0); (420.0,1160.0); (420.0,1144.0); (416.0,1132.0); (402.0,1118.0)</t>
         </is>
       </c>
     </row>
@@ -820,35 +832,37 @@
           <t>Cap1</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>397</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>1024</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>534</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>1153</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>0.9370000000000001</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>17</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>[[443.0, 1043.0], [422.0, 1065.0], [414.0, 1082.0], [412.0, 1099.0], [416.0, 1114.0], [423.0, 1126.0], [443.0, 1142.0], [462.0, 1147.0], [490.0, 1144.0], [508.0, 1124.0], [514.0, 1113.0], [518.0, 1093.0], [516.0, 1078.0], [503.0, 1055.0], [495.0, 1048.0], [472.0, 1040.0], [454.0, 1040.0]]</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>(443.0,1043.0); (422.0,1065.0); (414.0,1082.0); (412.0,1099.0); (416.0,1114.0); (423.0,1126.0); (443.0,1142.0); (462.0,1147.0); (490.0,1144.0); (508.0,1124.0); (514.0,1113.0); (518.0,1093.0); (516.0,1078.0); (503.0,1055.0); (495.0,1048.0); (472.0,1040.0); (454.0,1040.0)</t>
         </is>
       </c>
     </row>
@@ -871,35 +885,37 @@
           <t>Transformer</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Transformer_SMD</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Transformer_SMD:Transformer_Wuerth_WE-PoE_EP13</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>366</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>842</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>618</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1054</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>0.891</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>23</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>[[366.0, 883.0], [366.0, 899.0], [380.0, 919.0], [425.0, 896.0], [399.0, 938.0], [398.0, 961.0], [483.0, 1031.0], [521.0, 1036.0], [537.0, 1013.0], [562.0, 1021.0], [581.0, 997.0], [582.0, 988.0], [566.0, 974.0], [581.0, 956.0], [581.0, 932.0], [498.0, 870.0], [464.0, 862.0], [448.0, 869.0], [446.0, 885.0], [436.0, 889.0], [438.0, 862.0], [432.0, 842.0], [422.0, 841.0]]</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>(366.0,883.0); (366.0,899.0); (380.0,919.0); (425.0,896.0); (399.0,938.0); (398.0,961.0); (483.0,1031.0); (521.0,1036.0); (537.0,1013.0); (562.0,1021.0); (581.0,997.0); (582.0,988.0); (566.0,974.0); (581.0,956.0); (581.0,932.0); (498.0,870.0); (464.0,862.0); (448.0,869.0); (446.0,885.0); (436.0,889.0); (438.0,862.0); (432.0,842.0); (422.0,841.0)</t>
         </is>
       </c>
     </row>
@@ -922,35 +938,3535 @@
           <t>Mov</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Diode_SMD</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diode_SMD:D_SOD-123</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>651</v>
+      </c>
+      <c r="H10" t="n">
+        <v>856</v>
+      </c>
+      <c r="I10" t="n">
+        <v>826</v>
+      </c>
+      <c r="J10" t="n">
+        <v>986</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="L10" t="n">
+        <v>17</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>[[679.0, 871.0], [674.0, 890.0], [684.0, 904.0], [687.0, 917.0], [692.0, 922.0], [725.0, 937.0], [741.0, 951.0], [762.0, 962.0], [781.0, 966.0], [789.0, 961.0], [795.0, 952.0], [797.0, 938.0], [783.0, 917.0], [757.0, 894.0], [726.0, 874.0], [703.0, 864.0], [689.0, 864.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>VID20210601143927-96_jpg.rf.aa22533cba06977878022a9bb246d71c.jpg</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Resistor_SMD</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>700</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1194</v>
+      </c>
+      <c r="I11" t="n">
+        <v>774</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1280</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="L11" t="n">
+        <v>18</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>[[744.0, 1203.0], [732.0, 1201.0], [713.0, 1201.0], [710.0, 1203.0], [709.0, 1213.0], [712.0, 1229.0], [712.0, 1245.0], [709.0, 1258.0], [709.0, 1274.0], [715.0, 1279.0], [719.0, 1280.0], [724.0, 1278.0], [727.0, 1274.0], [743.0, 1272.0], [751.0, 1265.0], [760.0, 1252.0], [761.0, 1230.0], [749.0, 1207.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>VID20210601143927-96_jpg.rf.aa22533cba06977878022a9bb246d71c.jpg</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MOSFET</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD:SOT-23</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>603</v>
+      </c>
+      <c r="H12" t="n">
+        <v>846</v>
+      </c>
+      <c r="I12" t="n">
+        <v>744</v>
+      </c>
+      <c r="J12" t="n">
+        <v>998</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="L12" t="n">
+        <v>18</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>[[657.0, 873.0], [650.0, 880.0], [652.0, 893.0], [649.0, 913.0], [641.0, 927.0], [637.0, 948.0], [638.0, 955.0], [643.0, 959.0], [632.0, 965.0], [615.0, 968.0], [612.0, 991.0], [614.0, 994.0], [690.0, 1002.0], [696.0, 990.0], [694.0, 974.0], [707.0, 967.0], [721.0, 890.0], [706.0, 877.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>VID20210601143927-96_jpg.rf.aa22533cba06977878022a9bb246d71c.jpg</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Transformer_SMD</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Transformer_SMD:Transformer_Wuerth_WE-PoE_EP13</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>660</v>
+      </c>
+      <c r="H13" t="n">
+        <v>968</v>
+      </c>
+      <c r="I13" t="n">
+        <v>892</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1198</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="L13" t="n">
+        <v>30</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>[[713.0, 1017.0], [704.0, 1076.0], [709.0, 1124.0], [681.0, 1126.0], [670.0, 1134.0], [670.0, 1183.0], [681.0, 1193.0], [710.0, 1200.0], [842.0, 1209.0], [849.0, 1174.0], [831.0, 1152.0], [841.0, 1135.0], [839.0, 1116.0], [807.0, 1115.0], [800.0, 1105.0], [780.0, 1112.0], [771.0, 1104.0], [726.0, 1107.0], [713.0, 1101.0], [714.0, 1090.0], [725.0, 1081.0], [735.0, 1088.0], [758.0, 1088.0], [763.0, 1068.0], [784.0, 1076.0], [797.0, 1055.0], [791.0, 1040.0], [773.0, 1025.0], [757.0, 1033.0], [746.0, 1022.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>VID20210601143927-96_jpg.rf.aa22533cba06977878022a9bb246d71c.jpg</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Cap3</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>739</v>
+      </c>
+      <c r="H14" t="n">
+        <v>880</v>
+      </c>
+      <c r="I14" t="n">
+        <v>926</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1064</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>[[765.0, 926.0], [755.0, 946.0], [757.0, 966.0], [761.0, 974.0], [778.0, 994.0], [793.0, 1000.0], [823.0, 1022.0], [838.0, 1029.0], [854.0, 1029.0], [878.0, 1020.0], [893.0, 1005.0], [901.0, 985.0], [901.0, 963.0], [893.0, 945.0], [875.0, 930.0], [810.0, 905.0], [786.0, 909.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VID20210601143927-96_jpg.rf.aa22533cba06977878022a9bb246d71c.jpg</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>5</v>
       </c>
-      <c r="F10" t="n">
-        <v>651</v>
-      </c>
-      <c r="G10" t="n">
-        <v>856</v>
-      </c>
-      <c r="H10" t="n">
-        <v>826</v>
-      </c>
-      <c r="I10" t="n">
-        <v>986</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.9409999999999999</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Cap4</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>738</v>
+      </c>
+      <c r="H15" t="n">
+        <v>771</v>
+      </c>
+      <c r="I15" t="n">
+        <v>928</v>
+      </c>
+      <c r="J15" t="n">
+        <v>949</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="L15" t="n">
+        <v>18</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>[[746.0, 807.0], [743.0, 818.0], [747.0, 833.0], [780.0, 882.0], [804.0, 894.0], [833.0, 916.0], [854.0, 917.0], [876.0, 908.0], [890.0, 898.0], [897.0, 888.0], [903.0, 871.0], [902.0, 846.0], [893.0, 829.0], [876.0, 816.0], [847.0, 809.0], [821.0, 797.0], [781.0, 812.0], [759.0, 804.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>VID20210601143927-96_jpg.rf.aa22533cba06977878022a9bb246d71c.jpg</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Cap2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>210</v>
+      </c>
+      <c r="H16" t="n">
+        <v>892</v>
+      </c>
+      <c r="I16" t="n">
+        <v>312</v>
+      </c>
+      <c r="J16" t="n">
+        <v>994</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>[[679.0, 871.0], [674.0, 890.0], [684.0, 904.0], [687.0, 917.0], [692.0, 922.0], [725.0, 937.0], [741.0, 951.0], [762.0, 962.0], [781.0, 966.0], [789.0, 961.0], [795.0, 952.0], [797.0, 938.0], [783.0, 917.0], [757.0, 894.0], [726.0, 874.0], [703.0, 864.0], [689.0, 864.0]]</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>(679.0,871.0); (674.0,890.0); (684.0,904.0); (687.0,917.0); (692.0,922.0); (725.0,937.0); (741.0,951.0); (762.0,962.0); (781.0,966.0); (789.0,961.0); (795.0,952.0); (797.0,938.0); (783.0,917.0); (757.0,894.0); (726.0,874.0); (703.0,864.0); (689.0,864.0)</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>[[284.0, 911.0], [267.0, 909.0], [258.0, 910.0], [239.0, 919.0], [235.0, 924.0], [230.0, 937.0], [230.0, 951.0], [236.0, 967.0], [243.0, 974.0], [253.0, 979.0], [265.0, 981.0], [279.0, 977.0], [292.0, 965.0], [296.0, 953.0], [298.0, 934.0], [292.0, 919.0], [288.0, 913.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>VID20210601143927-96_jpg.rf.aa22533cba06977878022a9bb246d71c.jpg</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Cap1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>287</v>
+      </c>
+      <c r="H17" t="n">
+        <v>914</v>
+      </c>
+      <c r="I17" t="n">
+        <v>424</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1058</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="L17" t="n">
+        <v>23</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>[[386.0, 942.0], [368.0, 939.0], [360.0, 934.0], [337.0, 936.0], [323.0, 941.0], [313.0, 950.0], [301.0, 971.0], [299.0, 991.0], [305.0, 1010.0], [316.0, 1029.0], [310.0, 1038.0], [303.0, 1032.0], [294.0, 1032.0], [294.0, 1043.0], [310.0, 1048.0], [313.0, 1041.0], [321.0, 1037.0], [359.0, 1040.0], [378.0, 1033.0], [389.0, 1025.0], [403.0, 1003.0], [404.0, 982.0], [398.0, 959.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>VID20210601143927-96_jpg.rf.aa22533cba06977878022a9bb246d71c.jpg</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>8</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Transformer_SMD</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Transformer_SMD:Transformer_Wuerth_WE-PoE_EP13</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>378</v>
+      </c>
+      <c r="H18" t="n">
+        <v>810</v>
+      </c>
+      <c r="I18" t="n">
+        <v>604</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1072</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="L18" t="n">
+        <v>14</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>[[482.0, 843.0], [477.0, 853.0], [450.0, 854.0], [432.0, 871.0], [421.0, 929.0], [417.0, 988.0], [425.0, 1006.0], [435.0, 1012.0], [459.0, 1014.0], [469.0, 920.0], [473.0, 912.0], [473.0, 879.0], [476.0, 866.0], [489.0, 854.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>VID20210601143927-96_jpg.rf.aa22533cba06977878022a9bb246d71c.jpg</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mov</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Diode_SMD</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Diode_SMD:D_SOD-123</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>564</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1054</v>
+      </c>
+      <c r="I19" t="n">
+        <v>704</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1234</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="L19" t="n">
+        <v>18</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>[[584.0, 1061.0], [578.0, 1070.0], [581.0, 1079.0], [606.0, 1081.0], [597.0, 1100.0], [593.0, 1119.0], [594.0, 1184.0], [599.0, 1196.0], [610.0, 1203.0], [628.0, 1208.0], [643.0, 1207.0], [653.0, 1198.0], [664.0, 1169.0], [670.0, 1125.0], [666.0, 1080.0], [659.0, 1070.0], [651.0, 1066.0], [615.0, 1066.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>VID20210601143927-96_jpg.rf.be5e4aeaa0b8114ebc3dbb96b69a78b9.jpg</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Resistor_SMD</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>760</v>
+      </c>
+      <c r="H20" t="n">
+        <v>694</v>
+      </c>
+      <c r="I20" t="n">
+        <v>843</v>
+      </c>
+      <c r="J20" t="n">
+        <v>765</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="L20" t="n">
+        <v>18</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>[[771.0, 719.0], [767.0, 736.0], [767.0, 753.0], [769.0, 756.0], [792.0, 753.0], [808.0, 753.0], [813.0, 755.0], [822.0, 753.0], [835.0, 758.0], [839.0, 755.0], [841.0, 748.0], [836.0, 742.0], [836.0, 724.0], [819.0, 708.0], [799.0, 705.0], [789.0, 709.0], [784.0, 714.0], [775.0, 716.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>VID20210601143927-96_jpg.rf.be5e4aeaa0b8114ebc3dbb96b69a78b9.jpg</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MOSFET</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD:SOT-23</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>410</v>
+      </c>
+      <c r="H21" t="n">
+        <v>713</v>
+      </c>
+      <c r="I21" t="n">
+        <v>560</v>
+      </c>
+      <c r="J21" t="n">
+        <v>851</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="L21" t="n">
+        <v>22</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>[[451.0, 736.0], [441.0, 748.0], [435.0, 781.0], [435.0, 793.0], [442.0, 805.0], [478.0, 806.0], [486.0, 814.0], [505.0, 815.0], [512.0, 820.0], [523.0, 815.0], [527.0, 819.0], [530.0, 842.0], [552.0, 845.0], [559.0, 822.0], [565.0, 778.0], [558.0, 759.0], [538.0, 764.0], [533.0, 749.0], [527.0, 746.0], [479.0, 737.0], [467.0, 738.0], [460.0, 734.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>VID20210601143927-96_jpg.rf.be5e4aeaa0b8114ebc3dbb96b69a78b9.jpg</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Transformer_SMD</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Transformer_SMD:Transformer_Wuerth_WE-PoE_EP13</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>536</v>
+      </c>
+      <c r="H22" t="n">
+        <v>572</v>
+      </c>
+      <c r="I22" t="n">
+        <v>763</v>
+      </c>
+      <c r="J22" t="n">
+        <v>799</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="L22" t="n">
+        <v>24</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>[[618.0, 613.0], [602.0, 643.0], [614.0, 663.0], [591.0, 689.0], [599.0, 698.0], [582.0, 747.0], [654.0, 758.0], [697.0, 753.0], [695.0, 786.0], [734.0, 797.0], [750.0, 793.0], [766.0, 744.0], [778.0, 623.0], [742.0, 616.0], [720.0, 633.0], [707.0, 623.0], [689.0, 623.0], [672.0, 740.0], [652.0, 748.0], [641.0, 735.0], [646.0, 684.0], [655.0, 677.0], [648.0, 670.0], [653.0, 615.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>VID20210601143927-96_jpg.rf.be5e4aeaa0b8114ebc3dbb96b69a78b9.jpg</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Cap3</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>451</v>
+      </c>
+      <c r="H23" t="n">
+        <v>533</v>
+      </c>
+      <c r="I23" t="n">
+        <v>632</v>
+      </c>
+      <c r="J23" t="n">
+        <v>717</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="L23" t="n">
+        <v>15</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>[[565.0, 559.0], [538.0, 556.0], [514.0, 565.0], [502.0, 579.0], [488.0, 623.0], [476.0, 640.0], [477.0, 671.0], [493.0, 690.0], [508.0, 699.0], [536.0, 698.0], [557.0, 685.0], [596.0, 626.0], [599.0, 603.0], [592.0, 582.0], [579.0, 567.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>VID20210601143927-96_jpg.rf.be5e4aeaa0b8114ebc3dbb96b69a78b9.jpg</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Cap4</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>342</v>
+      </c>
+      <c r="H24" t="n">
+        <v>526</v>
+      </c>
+      <c r="I24" t="n">
+        <v>516</v>
+      </c>
+      <c r="J24" t="n">
+        <v>714</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="L24" t="n">
+        <v>18</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>[[463.0, 559.0], [441.0, 550.0], [424.0, 550.0], [403.0, 558.0], [389.0, 573.0], [366.0, 627.0], [367.0, 640.0], [380.0, 667.0], [368.0, 696.0], [373.0, 704.0], [398.0, 708.0], [408.0, 697.0], [449.0, 676.0], [461.0, 655.0], [479.0, 634.0], [488.0, 617.0], [487.0, 602.0], [478.0, 576.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>VID20210601143927-96_jpg.rf.be5e4aeaa0b8114ebc3dbb96b69a78b9.jpg</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Cap2</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>442</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1146</v>
+      </c>
+      <c r="I25" t="n">
+        <v>542</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1246</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="L25" t="n">
+        <v>16</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>[[472.0, 1161.0], [462.0, 1171.0], [463.0, 1209.0], [466.0, 1215.0], [462.0, 1224.0], [466.0, 1226.0], [471.0, 1223.0], [492.0, 1230.0], [513.0, 1229.0], [520.0, 1220.0], [529.0, 1202.0], [530.0, 1190.0], [527.0, 1179.0], [517.0, 1166.0], [507.0, 1160.0], [483.0, 1157.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>VID20210601143927-96_jpg.rf.be5e4aeaa0b8114ebc3dbb96b69a78b9.jpg</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>7</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Cap1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>468</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1036</v>
+      </c>
+      <c r="I26" t="n">
+        <v>609</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1170</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="L26" t="n">
+        <v>22</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>[[494.0, 1073.0], [492.0, 1079.0], [496.0, 1093.0], [492.0, 1098.0], [492.0, 1110.0], [488.0, 1122.0], [493.0, 1135.0], [509.0, 1151.0], [528.0, 1159.0], [550.0, 1159.0], [561.0, 1155.0], [573.0, 1145.0], [579.0, 1147.0], [589.0, 1145.0], [586.0, 1133.0], [592.0, 1113.0], [590.0, 1092.0], [581.0, 1073.0], [565.0, 1059.0], [547.0, 1052.0], [527.0, 1053.0], [512.0, 1059.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>VID20210601143927-96_jpg.rf.be5e4aeaa0b8114ebc3dbb96b69a78b9.jpg</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Transformer_SMD</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Transformer_SMD:Transformer_Wuerth_WE-PoE_EP13</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>369</v>
+      </c>
+      <c r="H27" t="n">
+        <v>855</v>
+      </c>
+      <c r="I27" t="n">
+        <v>627</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1076</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="L27" t="n">
+        <v>14</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>[[417.0, 928.0], [420.0, 933.0], [477.0, 937.0], [576.0, 953.0], [581.0, 948.0], [582.0, 922.0], [574.0, 921.0], [570.0, 910.0], [558.0, 906.0], [460.0, 892.0], [455.0, 895.0], [441.0, 895.0], [432.0, 903.0], [420.0, 908.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>VID20210601143927-96_jpg.rf.be5e4aeaa0b8114ebc3dbb96b69a78b9.jpg</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>9</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Mov</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Diode_SMD</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Diode_SMD:D_SOD-123</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>617</v>
+      </c>
+      <c r="H28" t="n">
+        <v>761</v>
+      </c>
+      <c r="I28" t="n">
+        <v>795</v>
+      </c>
+      <c r="J28" t="n">
+        <v>898</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="L28" t="n">
+        <v>17</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>[[630.0, 808.0], [630.0, 834.0], [642.0, 845.0], [644.0, 853.0], [661.0, 866.0], [683.0, 867.0], [696.0, 872.0], [703.0, 869.0], [730.0, 873.0], [746.0, 872.0], [757.0, 865.0], [769.0, 840.0], [769.0, 822.0], [739.0, 803.0], [683.0, 792.0], [660.0, 792.0], [639.0, 797.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>VID20210601144029-63_jpg.rf.3ea588252f27b0731ac71d861be3e140.jpg</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Transformer_SMD</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Transformer_SMD:Transformer_Wuerth_WE-PoE_EP13</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1117</v>
+      </c>
+      <c r="H29" t="n">
+        <v>801</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1367</v>
+      </c>
+      <c r="J29" t="n">
+        <v>929</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="L29" t="n">
+        <v>18</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>[[1136.0, 848.0], [1136.0, 868.0], [1156.0, 901.0], [1183.0, 919.0], [1284.0, 911.0], [1309.0, 903.0], [1340.0, 902.0], [1347.0, 894.0], [1346.0, 868.0], [1321.0, 853.0], [1312.0, 853.0], [1305.0, 864.0], [1297.0, 867.0], [1254.0, 864.0], [1243.0, 872.0], [1185.0, 877.0], [1163.0, 854.0], [1145.0, 845.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>VID20210601144029-63_jpg.rf.3ea588252f27b0731ac71d861be3e140.jpg</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Cap1</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>660</v>
+      </c>
+      <c r="H30" t="n">
+        <v>717</v>
+      </c>
+      <c r="I30" t="n">
+        <v>800</v>
+      </c>
+      <c r="J30" t="n">
+        <v>920</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="L30" t="n">
+        <v>18</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>[[698.0, 745.0], [670.0, 757.0], [659.0, 767.0], [652.0, 781.0], [660.0, 822.0], [667.0, 832.0], [668.0, 866.0], [676.0, 886.0], [689.0, 898.0], [711.0, 909.0], [744.0, 911.0], [771.0, 898.0], [789.0, 876.0], [796.0, 852.0], [793.0, 824.0], [761.0, 780.0], [753.0, 758.0], [738.0, 747.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>VID20210601144029-63_jpg.rf.3ea588252f27b0731ac71d861be3e140.jpg</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Cap2</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>554</v>
+      </c>
+      <c r="H31" t="n">
+        <v>718</v>
+      </c>
+      <c r="I31" t="n">
+        <v>660</v>
+      </c>
+      <c r="J31" t="n">
+        <v>858</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="L31" t="n">
+        <v>20</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>[[573.0, 737.0], [567.0, 741.0], [559.0, 753.0], [556.0, 773.0], [563.0, 793.0], [572.0, 805.0], [578.0, 835.0], [584.0, 842.0], [599.0, 851.0], [627.0, 851.0], [638.0, 845.0], [653.0, 828.0], [657.0, 809.0], [654.0, 796.0], [647.0, 783.0], [635.0, 777.0], [627.0, 750.0], [618.0, 734.0], [598.0, 730.0], [581.0, 737.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>VID20210601144029-63_jpg.rf.3ea588252f27b0731ac71d861be3e140.jpg</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Cap3</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1170</v>
+      </c>
+      <c r="H32" t="n">
+        <v>670</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1383</v>
+      </c>
+      <c r="J32" t="n">
+        <v>807</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="L32" t="n">
+        <v>24</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>[[1175.0, 670.0], [1172.0, 692.0], [1183.0, 719.0], [1292.0, 795.0], [1316.0, 799.0], [1333.0, 794.0], [1356.0, 780.0], [1371.0, 759.0], [1376.0, 724.0], [1369.0, 706.0], [1350.0, 689.0], [1308.0, 680.0], [1286.0, 669.0], [1278.0, 678.0], [1291.0, 683.0], [1302.0, 699.0], [1285.0, 706.0], [1272.0, 688.0], [1252.0, 684.0], [1245.0, 690.0], [1279.0, 701.0], [1279.0, 717.0], [1272.0, 719.0], [1188.0, 666.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>VID20210601144029-63_jpg.rf.3ea588252f27b0731ac71d861be3e140.jpg</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>MOSFET</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD:SOT-23</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1022</v>
+      </c>
+      <c r="H33" t="n">
+        <v>615</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1138</v>
+      </c>
+      <c r="J33" t="n">
+        <v>739</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="L33" t="n">
+        <v>13</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>[[1053.0, 622.0], [1043.0, 635.0], [1044.0, 664.0], [1039.0, 699.0], [1041.0, 731.0], [1083.0, 736.0], [1089.0, 729.0], [1114.0, 728.0], [1117.0, 723.0], [1121.0, 678.0], [1122.0, 626.0], [1107.0, 624.0], [1101.0, 620.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>VID20210601144029-63_jpg.rf.3ea588252f27b0731ac71d861be3e140.jpg</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>6</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Cap4</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1178</v>
+      </c>
+      <c r="H34" t="n">
+        <v>498</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1388</v>
+      </c>
+      <c r="J34" t="n">
+        <v>682</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="L34" t="n">
+        <v>19</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>[[1186.0, 533.0], [1177.0, 568.0], [1190.0, 574.0], [1188.0, 558.0], [1199.0, 562.0], [1203.0, 586.0], [1194.0, 600.0], [1197.0, 607.0], [1269.0, 642.0], [1307.0, 671.0], [1337.0, 672.0], [1357.0, 663.0], [1384.0, 630.0], [1389.0, 602.0], [1384.0, 581.0], [1372.0, 565.0], [1353.0, 554.0], [1240.0, 510.0], [1204.0, 518.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>VID20210601144029-63_jpg.rf.3ea588252f27b0731ac71d861be3e140.jpg</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Mov</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Diode_SMD</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Diode_SMD:D_SOD-123</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>959</v>
+      </c>
+      <c r="H35" t="n">
+        <v>871</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1060</v>
+      </c>
+      <c r="J35" t="n">
+        <v>984</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="L35" t="n">
+        <v>19</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>[[1015.0, 880.0], [1011.0, 880.0], [1003.0, 886.0], [997.0, 898.0], [997.0, 907.0], [979.0, 978.0], [982.0, 984.0], [1042.0, 983.0], [1047.0, 981.0], [1049.0, 976.0], [1049.0, 966.0], [1044.0, 960.0], [1042.0, 950.0], [1042.0, 925.0], [1045.0, 916.0], [1039.0, 910.0], [1040.0, 904.0], [1032.0, 903.0], [1027.0, 899.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>VID20210601144029-63_jpg.rf.48a3a71137ec74a925e766c1992f1235.jpg</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Transformer_SMD</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Transformer_SMD:Transformer_Wuerth_WE-PoE_EP13</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>380</v>
+      </c>
+      <c r="H36" t="n">
+        <v>854</v>
+      </c>
+      <c r="I36" t="n">
+        <v>636</v>
+      </c>
+      <c r="J36" t="n">
+        <v>994</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="L36" t="n">
+        <v>22</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>[[612.0, 894.0], [604.0, 884.0], [590.0, 889.0], [574.0, 919.0], [556.0, 927.0], [512.0, 928.0], [500.0, 922.0], [482.0, 921.0], [464.0, 930.0], [434.0, 931.0], [424.0, 927.0], [408.0, 936.0], [409.0, 964.0], [416.0, 970.0], [450.0, 970.0], [465.0, 982.0], [561.0, 974.0], [585.0, 978.0], [590.0, 956.0], [608.0, 949.0], [612.0, 942.0], [609.0, 927.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>VID20210601144029-63_jpg.rf.48a3a71137ec74a925e766c1992f1235.jpg</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Cap1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>935</v>
+      </c>
+      <c r="H37" t="n">
+        <v>710</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1086</v>
+      </c>
+      <c r="J37" t="n">
+        <v>919</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="L37" t="n">
+        <v>18</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>[[1059.0, 741.0], [1029.0, 738.0], [993.0, 744.0], [979.0, 760.0], [974.0, 782.0], [949.0, 825.0], [953.0, 867.0], [967.0, 887.0], [988.0, 902.0], [1024.0, 907.0], [1045.0, 900.0], [1066.0, 884.0], [1074.0, 872.0], [1078.0, 852.0], [1075.0, 821.0], [1082.0, 808.0], [1086.0, 771.0], [1081.0, 759.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>VID20210601144029-63_jpg.rf.48a3a71137ec74a925e766c1992f1235.jpg</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>3</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Cap2</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1072</v>
+      </c>
+      <c r="H38" t="n">
+        <v>698</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1185</v>
+      </c>
+      <c r="J38" t="n">
+        <v>842</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="L38" t="n">
+        <v>18</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>[[1157.0, 713.0], [1126.0, 711.0], [1114.0, 716.0], [1104.0, 733.0], [1101.0, 757.0], [1087.0, 773.0], [1083.0, 784.0], [1083.0, 798.0], [1088.0, 813.0], [1109.0, 832.0], [1120.0, 835.0], [1142.0, 832.0], [1155.0, 824.0], [1164.0, 812.0], [1166.0, 779.0], [1174.0, 766.0], [1176.0, 740.0], [1171.0, 727.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>VID20210601144029-63_jpg.rf.48a3a71137ec74a925e766c1992f1235.jpg</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Cap3</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>349</v>
+      </c>
+      <c r="H39" t="n">
+        <v>728</v>
+      </c>
+      <c r="I39" t="n">
+        <v>569</v>
+      </c>
+      <c r="J39" t="n">
+        <v>876</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="L39" t="n">
+        <v>20</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>[[562.0, 723.0], [542.0, 720.0], [459.0, 785.0], [448.0, 784.0], [417.0, 760.0], [456.0, 745.0], [453.0, 737.0], [472.0, 722.0], [444.0, 730.0], [420.0, 749.0], [381.0, 760.0], [368.0, 772.0], [360.0, 791.0], [366.0, 830.0], [382.0, 849.0], [408.0, 863.0], [429.0, 866.0], [452.0, 859.0], [557.0, 765.0], [564.0, 748.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>VID20210601144029-63_jpg.rf.48a3a71137ec74a925e766c1992f1235.jpg</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>5</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>MOSFET</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD:SOT-23</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>586</v>
+      </c>
+      <c r="H40" t="n">
+        <v>653</v>
+      </c>
+      <c r="I40" t="n">
+        <v>708</v>
+      </c>
+      <c r="J40" t="n">
+        <v>782</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.954</v>
+      </c>
+      <c r="L40" t="n">
+        <v>19</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>[[667.0, 658.0], [631.0, 662.0], [625.0, 666.0], [603.0, 668.0], [597.0, 674.0], [613.0, 761.0], [619.0, 771.0], [642.0, 769.0], [654.0, 773.0], [682.0, 770.0], [689.0, 766.0], [690.0, 759.0], [687.0, 753.0], [690.0, 742.0], [689.0, 723.0], [682.0, 702.0], [681.0, 688.0], [674.0, 681.0], [677.0, 668.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>VID20210601144029-63_jpg.rf.48a3a71137ec74a925e766c1992f1235.jpg</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>6</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Cap4</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>324</v>
+      </c>
+      <c r="H41" t="n">
+        <v>560</v>
+      </c>
+      <c r="I41" t="n">
+        <v>544</v>
+      </c>
+      <c r="J41" t="n">
+        <v>752</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="L41" t="n">
+        <v>21</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>[[563.0, 579.0], [552.0, 575.0], [552.0, 593.0], [542.0, 595.0], [531.0, 583.0], [520.0, 583.0], [507.0, 572.0], [472.0, 569.0], [358.0, 629.0], [339.0, 646.0], [331.0, 667.0], [331.0, 683.0], [342.0, 710.0], [373.0, 737.0], [416.0, 739.0], [451.0, 704.0], [508.0, 675.0], [525.0, 660.0], [526.0, 647.0], [553.0, 598.0], [566.0, 592.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>VID20210601144029-63_jpg.rf.48a3a71137ec74a925e766c1992f1235.jpg</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>7</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Mov</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Diode_SMD</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Diode_SMD:D_SOD-123</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>694</v>
+      </c>
+      <c r="H42" t="n">
+        <v>898</v>
+      </c>
+      <c r="I42" t="n">
+        <v>802</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1005</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="L42" t="n">
+        <v>13</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>[[701.0, 885.0], [690.0, 899.0], [689.0, 915.0], [702.0, 969.0], [701.0, 979.0], [711.0, 1002.0], [715.0, 1005.0], [782.0, 1005.0], [777.0, 984.0], [767.0, 962.0], [759.0, 927.0], [746.0, 897.0], [731.0, 884.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>VID20210601144029-63_jpg.rf.958862ae4c7ea100804351bd294afe5d.jpg</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Transformer_SMD</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Transformer_SMD:Transformer_Wuerth_WE-PoE_EP13</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>426</v>
+      </c>
+      <c r="H43" t="n">
+        <v>8</v>
+      </c>
+      <c r="I43" t="n">
+        <v>548</v>
+      </c>
+      <c r="J43" t="n">
+        <v>256</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="L43" t="n">
+        <v>22</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>[[417.0, 0.0], [409.0, 9.0], [407.0, 57.0], [414.0, 66.0], [428.0, 68.0], [442.0, 43.0], [449.0, 78.0], [442.0, 109.0], [437.0, 195.0], [454.0, 209.0], [475.0, 207.0], [479.0, 131.0], [489.0, 108.0], [482.0, 91.0], [488.0, 61.0], [484.0, 39.0], [488.0, 30.0], [482.0, 17.0], [498.0, 15.0], [506.0, 26.0], [515.0, 9.0], [509.0, 0.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>VID20210601144029-63_jpg.rf.958862ae4c7ea100804351bd294afe5d.jpg</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Cap1</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>442</v>
+      </c>
+      <c r="H44" t="n">
+        <v>574</v>
+      </c>
+      <c r="I44" t="n">
+        <v>642</v>
+      </c>
+      <c r="J44" t="n">
+        <v>711</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="L44" t="n">
+        <v>21</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>[[472.0, 595.0], [455.0, 620.0], [450.0, 640.0], [456.0, 672.0], [471.0, 695.0], [518.0, 711.0], [541.0, 708.0], [543.0, 717.0], [555.0, 715.0], [576.0, 722.0], [591.0, 718.0], [610.0, 701.0], [613.0, 677.0], [610.0, 668.0], [617.0, 660.0], [619.0, 640.0], [604.0, 619.0], [584.0, 615.0], [545.0, 584.0], [534.0, 580.0], [505.0, 579.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>VID20210601144029-63_jpg.rf.958862ae4c7ea100804351bd294afe5d.jpg</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Cap2</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>506</v>
+      </c>
+      <c r="H45" t="n">
+        <v>714</v>
+      </c>
+      <c r="I45" t="n">
+        <v>644</v>
+      </c>
+      <c r="J45" t="n">
+        <v>816</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="L45" t="n">
+        <v>17</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>[[517.0, 738.0], [512.0, 757.0], [512.0, 772.0], [522.0, 790.0], [527.0, 794.0], [561.0, 804.0], [587.0, 818.0], [608.0, 817.0], [625.0, 806.0], [629.0, 796.0], [628.0, 786.0], [633.0, 767.0], [623.0, 751.0], [587.0, 737.0], [576.0, 723.0], [562.0, 717.0], [534.0, 722.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>VID20210601144029-63_jpg.rf.958862ae4c7ea100804351bd294afe5d.jpg</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Cap3</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>546</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>682</v>
+      </c>
+      <c r="J46" t="n">
+        <v>203</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="L46" t="n">
+        <v>23</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>[[591.0, 0.0], [567.0, 23.0], [555.0, 46.0], [556.0, 79.0], [638.0, 193.0], [665.0, 203.0], [684.0, 199.0], [689.0, 187.0], [672.0, 156.0], [694.0, 124.0], [687.0, 102.0], [684.0, 107.0], [686.0, 125.0], [681.0, 128.0], [668.0, 102.0], [650.0, 111.0], [638.0, 103.0], [657.0, 100.0], [660.0, 74.0], [671.0, 96.0], [681.0, 90.0], [661.0, 18.0], [642.0, 0.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>VID20210601144029-63_jpg.rf.958862ae4c7ea100804351bd294afe5d.jpg</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>MOSFET</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD:SOT-23</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>617</v>
+      </c>
+      <c r="H47" t="n">
+        <v>234</v>
+      </c>
+      <c r="I47" t="n">
+        <v>739</v>
+      </c>
+      <c r="J47" t="n">
+        <v>348</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L47" t="n">
+        <v>16</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>[[730.0, 249.0], [723.0, 246.0], [668.0, 253.0], [636.0, 254.0], [627.0, 257.0], [627.0, 278.0], [623.0, 289.0], [623.0, 316.0], [626.0, 326.0], [635.0, 334.0], [640.0, 330.0], [664.0, 332.0], [693.0, 326.0], [718.0, 329.0], [733.0, 321.0], [736.0, 301.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>VID20210601144029-63_jpg.rf.958862ae4c7ea100804351bd294afe5d.jpg</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>6</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Cap4</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>671</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>852</v>
+      </c>
+      <c r="J48" t="n">
+        <v>192</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="L48" t="n">
+        <v>16</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>[[699.0, 0.0], [681.0, 28.0], [678.0, 59.0], [695.0, 90.0], [717.0, 115.0], [736.0, 160.0], [752.0, 178.0], [767.0, 170.0], [785.0, 170.0], [793.0, 174.0], [790.0, 181.0], [797.0, 183.0], [829.0, 174.0], [842.0, 148.0], [841.0, 120.0], [789.0, 0.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>VID20210601144029-63_jpg.rf.958862ae4c7ea100804351bd294afe5d.jpg</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>7</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Mov</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Diode_SMD</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Diode_SMD:D_SOD-123</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>398</v>
+      </c>
+      <c r="H49" t="n">
+        <v>317</v>
+      </c>
+      <c r="I49" t="n">
+        <v>484</v>
+      </c>
+      <c r="J49" t="n">
+        <v>416</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="L49" t="n">
+        <v>18</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>[[493.0, 313.0], [482.0, 310.0], [406.0, 313.0], [403.0, 318.0], [405.0, 329.0], [401.0, 336.0], [400.0, 351.0], [401.0, 391.0], [408.0, 392.0], [440.0, 384.0], [456.0, 384.0], [477.0, 379.0], [485.0, 372.0], [494.0, 372.0], [497.0, 370.0], [497.0, 364.0], [505.0, 357.0], [506.0, 328.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.5f574c206f4167d15d73f58b9e2a4f51.jpg</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Transformer_SMD</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Transformer_SMD:Transformer_Wuerth_WE-PoE_EP13</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>1211</v>
+      </c>
+      <c r="H50" t="n">
+        <v>687</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1455</v>
+      </c>
+      <c r="J50" t="n">
+        <v>854</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="L50" t="n">
+        <v>24</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>[[1214.0, 715.0], [1219.0, 796.0], [1231.0, 794.0], [1253.0, 819.0], [1279.0, 836.0], [1291.0, 838.0], [1337.0, 825.0], [1382.0, 822.0], [1397.0, 807.0], [1433.0, 799.0], [1432.0, 771.0], [1395.0, 754.0], [1382.0, 721.0], [1362.0, 719.0], [1340.0, 709.0], [1331.0, 692.0], [1310.0, 693.0], [1310.0, 710.0], [1318.0, 713.0], [1313.0, 716.0], [1275.0, 696.0], [1267.0, 697.0], [1262.0, 717.0], [1235.0, 708.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.5f574c206f4167d15d73f58b9e2a4f51.jpg</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Cap1</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>774</v>
+      </c>
+      <c r="H51" t="n">
+        <v>707</v>
+      </c>
+      <c r="I51" t="n">
+        <v>929</v>
+      </c>
+      <c r="J51" t="n">
+        <v>908</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="L51" t="n">
+        <v>19</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>[[806.0, 734.0], [780.0, 748.0], [770.0, 758.0], [766.0, 779.0], [781.0, 800.0], [781.0, 827.0], [790.0, 830.0], [796.0, 856.0], [811.0, 879.0], [842.0, 891.0], [877.0, 887.0], [907.0, 863.0], [917.0, 831.0], [911.0, 798.0], [879.0, 763.0], [869.0, 760.0], [852.0, 736.0], [841.0, 736.0], [830.0, 730.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.5f574c206f4167d15d73f58b9e2a4f51.jpg</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>3</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Cap2</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>670</v>
+      </c>
+      <c r="H52" t="n">
+        <v>718</v>
+      </c>
+      <c r="I52" t="n">
+        <v>784</v>
+      </c>
+      <c r="J52" t="n">
+        <v>864</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="L52" t="n">
+        <v>20</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>[[694.0, 738.0], [678.0, 751.0], [673.0, 764.0], [673.0, 779.0], [684.0, 799.0], [698.0, 810.0], [705.0, 835.0], [715.0, 845.0], [729.0, 851.0], [746.0, 851.0], [765.0, 841.0], [776.0, 828.0], [780.0, 807.0], [779.0, 797.0], [771.0, 784.0], [763.0, 776.0], [754.0, 774.0], [740.0, 748.0], [728.0, 734.0], [713.0, 732.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.5f574c206f4167d15d73f58b9e2a4f51.jpg</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>4</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Transformer_SMD</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Transformer_SMD:Transformer_Wuerth_WE-PoE_EP13</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>891</v>
+      </c>
+      <c r="H53" t="n">
+        <v>586</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1087</v>
+      </c>
+      <c r="J53" t="n">
+        <v>889</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="L53" t="n">
+        <v>23</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>[[898.0, 626.0], [886.0, 649.0], [897.0, 658.0], [909.0, 686.0], [914.0, 763.0], [934.0, 776.0], [943.0, 793.0], [949.0, 834.0], [997.0, 835.0], [1000.0, 842.0], [992.0, 848.0], [1010.0, 867.0], [1054.0, 858.0], [1055.0, 815.0], [1092.0, 809.0], [1100.0, 796.0], [1091.0, 685.0], [1049.0, 689.0], [1040.0, 663.0], [1027.0, 650.0], [1040.0, 635.0], [1019.0, 613.0], [978.0, 607.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.5f574c206f4167d15d73f58b9e2a4f51.jpg</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>5</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Cap3</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>1236</v>
+      </c>
+      <c r="H54" t="n">
+        <v>542</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1462</v>
+      </c>
+      <c r="J54" t="n">
+        <v>738</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="L54" t="n">
+        <v>17</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>[[1247.0, 579.0], [1240.0, 607.0], [1240.0, 624.0], [1247.0, 636.0], [1259.0, 647.0], [1372.0, 708.0], [1396.0, 710.0], [1424.0, 694.0], [1440.0, 672.0], [1445.0, 655.0], [1444.0, 630.0], [1424.0, 603.0], [1403.0, 595.0], [1372.0, 593.0], [1318.0, 565.0], [1285.0, 555.0], [1261.0, 564.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.5f574c206f4167d15d73f58b9e2a4f51.jpg</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>6</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Resistor_SMD</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>1254</v>
+      </c>
+      <c r="H55" t="n">
+        <v>906</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1352</v>
+      </c>
+      <c r="J55" t="n">
+        <v>974</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="L55" t="n">
+        <v>14</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>[[1265.0, 928.0], [1276.0, 947.0], [1296.0, 967.0], [1305.0, 967.0], [1321.0, 961.0], [1328.0, 948.0], [1329.0, 944.0], [1328.0, 937.0], [1324.0, 933.0], [1320.0, 925.0], [1307.0, 915.0], [1300.0, 915.0], [1285.0, 918.0], [1271.0, 926.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.5f574c206f4167d15d73f58b9e2a4f51.jpg</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>7</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>MOSFET</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD:SOT-23</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>1096</v>
+      </c>
+      <c r="H56" t="n">
+        <v>542</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1219</v>
+      </c>
+      <c r="J56" t="n">
+        <v>683</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="L56" t="n">
+        <v>21</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>[[1172.0, 557.0], [1154.0, 559.0], [1167.0, 564.0], [1164.0, 566.0], [1145.0, 563.0], [1134.0, 567.0], [1123.0, 566.0], [1121.0, 569.0], [1119.0, 595.0], [1125.0, 605.0], [1123.0, 649.0], [1128.0, 657.0], [1125.0, 665.0], [1138.0, 678.0], [1162.0, 676.0], [1180.0, 668.0], [1199.0, 664.0], [1195.0, 573.0], [1190.0, 566.0], [1173.0, 565.0], [1175.0, 559.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.5f574c206f4167d15d73f58b9e2a4f51.jpg</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>8</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Cap4</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1228</v>
+      </c>
+      <c r="H57" t="n">
+        <v>416</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1460</v>
+      </c>
+      <c r="J57" t="n">
+        <v>612</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="L57" t="n">
+        <v>19</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>[[1224.0, 486.0], [1226.0, 499.0], [1239.0, 511.0], [1262.0, 506.0], [1267.0, 517.0], [1260.0, 535.0], [1269.0, 543.0], [1343.0, 565.0], [1353.0, 579.0], [1377.0, 591.0], [1402.0, 589.0], [1429.0, 566.0], [1440.0, 545.0], [1440.0, 502.0], [1423.0, 480.0], [1304.0, 442.0], [1284.0, 439.0], [1265.0, 445.0], [1236.0, 468.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.5f574c206f4167d15d73f58b9e2a4f51.jpg</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>9</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Mov</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Diode_SMD</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Diode_SMD:D_SOD-123</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1068</v>
+      </c>
+      <c r="H58" t="n">
+        <v>800</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1202</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L58" t="n">
+        <v>14</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>[[1152.0, 790.0], [1110.0, 799.0], [1104.0, 813.0], [1102.0, 966.0], [1106.0, 993.0], [1111.0, 996.0], [1144.0, 989.0], [1151.0, 948.0], [1162.0, 922.0], [1164.0, 897.0], [1170.0, 892.0], [1173.0, 849.0], [1169.0, 817.0], [1163.0, 799.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.7b102fd7d6fd43e78519d57c295fa7ca.jpg</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Transformer_SMD</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Transformer_SMD:Transformer_Wuerth_WE-PoE_EP13</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>516</v>
+      </c>
+      <c r="H59" t="n">
+        <v>830</v>
+      </c>
+      <c r="I59" t="n">
+        <v>753</v>
+      </c>
+      <c r="J59" t="n">
+        <v>982</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="L59" t="n">
+        <v>25</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>[[736.0, 825.0], [714.0, 823.0], [708.0, 843.0], [694.0, 842.0], [679.0, 817.0], [643.0, 847.0], [643.0, 827.0], [627.0, 827.0], [623.0, 831.0], [626.0, 839.0], [612.0, 846.0], [607.0, 856.0], [575.0, 872.0], [574.0, 905.0], [541.0, 927.0], [546.0, 957.0], [584.0, 958.0], [599.0, 969.0], [616.0, 969.0], [638.0, 960.0], [706.0, 957.0], [726.0, 935.0], [738.0, 905.0], [732.0, 864.0], [722.0, 832.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.7b102fd7d6fd43e78519d57c295fa7ca.jpg</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>2</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Cap1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1040</v>
+      </c>
+      <c r="H60" t="n">
+        <v>728</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1182</v>
+      </c>
+      <c r="J60" t="n">
+        <v>922</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="L60" t="n">
+        <v>21</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>[[1159.0, 746.0], [1124.0, 743.0], [1114.0, 745.0], [1106.0, 755.0], [1093.0, 757.0], [1088.0, 778.0], [1078.0, 785.0], [1053.0, 831.0], [1053.0, 859.0], [1057.0, 871.0], [1074.0, 894.0], [1092.0, 904.0], [1111.0, 909.0], [1142.0, 904.0], [1171.0, 879.0], [1176.0, 863.0], [1176.0, 830.0], [1182.0, 821.0], [1180.0, 794.0], [1188.0, 771.0], [1177.0, 757.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.7b102fd7d6fd43e78519d57c295fa7ca.jpg</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>3</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Cap2</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1175</v>
+      </c>
+      <c r="H61" t="n">
+        <v>709</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1280</v>
+      </c>
+      <c r="J61" t="n">
+        <v>850</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="L61" t="n">
+        <v>20</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>[[1255.0, 721.0], [1227.0, 719.0], [1217.0, 722.0], [1208.0, 738.0], [1199.0, 769.0], [1187.0, 778.0], [1182.0, 788.0], [1181.0, 804.0], [1187.0, 821.0], [1197.0, 833.0], [1219.0, 841.0], [1234.0, 840.0], [1251.0, 831.0], [1261.0, 817.0], [1263.0, 805.0], [1261.0, 788.0], [1274.0, 774.0], [1279.0, 755.0], [1274.0, 737.0], [1268.0, 729.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.7b102fd7d6fd43e78519d57c295fa7ca.jpg</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>4</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Transformer_SMD</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Transformer_SMD:Transformer_Wuerth_WE-PoE_EP13</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>871</v>
+      </c>
+      <c r="H62" t="n">
+        <v>644</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1050</v>
+      </c>
+      <c r="J62" t="n">
+        <v>937</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="L62" t="n">
+        <v>36</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>[[999.0, 658.0], [933.0, 663.0], [932.0, 675.0], [912.0, 670.0], [902.0, 678.0], [925.0, 679.0], [895.0, 730.0], [894.0, 755.0], [882.0, 760.0], [897.0, 765.0], [891.0, 811.0], [929.0, 924.0], [976.0, 919.0], [976.0, 868.0], [994.0, 873.0], [990.0, 885.0], [1024.0, 875.0], [1018.0, 831.0], [1036.0, 789.0], [1034.0, 748.0], [1027.0, 754.0], [1019.0, 741.0], [1015.0, 754.0], [995.0, 752.0], [1003.0, 757.0], [1008.0, 856.0], [996.0, 865.0], [976.0, 861.0], [962.0, 763.0], [950.0, 747.0], [955.0, 734.0], [961.0, 741.0], [977.0, 725.0], [983.0, 706.0], [973.0, 707.0], [972.0, 696.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.7b102fd7d6fd43e78519d57c295fa7ca.jpg</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>5</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Cap3</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>479</v>
+      </c>
+      <c r="H63" t="n">
+        <v>692</v>
+      </c>
+      <c r="I63" t="n">
+        <v>696</v>
+      </c>
+      <c r="J63" t="n">
+        <v>874</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="L63" t="n">
+        <v>15</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>[[678.0, 708.0], [652.0, 688.0], [634.0, 685.0], [562.0, 740.0], [513.0, 760.0], [502.0, 772.0], [495.0, 793.0], [498.0, 816.0], [510.0, 837.0], [528.0, 852.0], [551.0, 861.0], [570.0, 861.0], [583.0, 855.0], [681.0, 764.0], [687.0, 728.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.7b102fd7d6fd43e78519d57c295fa7ca.jpg</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>6</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Resistor_SMD</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>658</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1031</v>
+      </c>
+      <c r="I64" t="n">
+        <v>752</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1045</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="L64" t="n">
+        <v>11</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>[[657.0, 1041.0], [659.0, 1045.0], [742.0, 1045.0], [747.0, 1041.0], [747.0, 1037.0], [749.0, 1036.0], [738.0, 1038.0], [723.0, 1036.0], [709.0, 1037.0], [671.0, 1036.0], [659.0, 1038.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.7b102fd7d6fd43e78519d57c295fa7ca.jpg</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>7</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>MOSFET</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD:SOT-23</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>709</v>
+      </c>
+      <c r="H65" t="n">
+        <v>642</v>
+      </c>
+      <c r="I65" t="n">
+        <v>825</v>
+      </c>
+      <c r="J65" t="n">
+        <v>778</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="L65" t="n">
+        <v>15</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>[[789.0, 657.0], [754.0, 658.0], [756.0, 664.0], [738.0, 666.0], [724.0, 673.0], [721.0, 678.0], [738.0, 764.0], [744.0, 771.0], [803.0, 769.0], [809.0, 764.0], [807.0, 749.0], [811.0, 743.0], [811.0, 735.0], [802.0, 702.0], [800.0, 678.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.7b102fd7d6fd43e78519d57c295fa7ca.jpg</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>8</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Cap4</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>450</v>
+      </c>
+      <c r="H66" t="n">
+        <v>568</v>
+      </c>
+      <c r="I66" t="n">
+        <v>675</v>
+      </c>
+      <c r="J66" t="n">
+        <v>752</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="L66" t="n">
+        <v>19</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>[[686.0, 580.0], [664.0, 580.0], [659.0, 587.0], [649.0, 589.0], [639.0, 578.0], [626.0, 573.0], [591.0, 576.0], [481.0, 643.0], [468.0, 670.0], [476.0, 709.0], [505.0, 738.0], [525.0, 745.0], [548.0, 741.0], [585.0, 703.0], [642.0, 673.0], [665.0, 650.0], [668.0, 629.0], [677.0, 611.0], [693.0, 597.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.7b102fd7d6fd43e78519d57c295fa7ca.jpg</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>9</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Mov</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Diode_SMD</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Diode_SMD:D_SOD-123</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>799</v>
+      </c>
+      <c r="H67" t="n">
+        <v>886</v>
+      </c>
+      <c r="I67" t="n">
+        <v>919</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1045</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="L67" t="n">
+        <v>14</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>[[816.0, 880.0], [807.0, 895.0], [814.0, 956.0], [818.0, 967.0], [825.0, 952.0], [835.0, 962.0], [826.0, 980.0], [840.0, 1015.0], [863.0, 1043.0], [906.0, 1045.0], [908.0, 1039.0], [868.0, 888.0], [859.0, 880.0], [850.0, 878.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.8b60a8acbaab729312e007c7c316e674.jpg</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Transformer_SMD</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Transformer_SMD:Transformer_Wuerth_WE-PoE_EP13</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>1198</v>
+      </c>
+      <c r="H68" t="n">
+        <v>180</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1444</v>
+      </c>
+      <c r="J68" t="n">
+        <v>354</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="L68" t="n">
+        <v>25</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>[[1204.0, 308.0], [1205.0, 313.0], [1211.0, 308.0], [1210.0, 317.0], [1232.0, 321.0], [1247.0, 315.0], [1253.0, 339.0], [1291.0, 321.0], [1296.0, 324.0], [1295.0, 340.0], [1312.0, 341.0], [1345.0, 318.0], [1368.0, 317.0], [1382.0, 283.0], [1416.0, 272.0], [1420.0, 241.0], [1387.0, 232.0], [1374.0, 220.0], [1324.0, 213.0], [1282.0, 199.0], [1266.0, 200.0], [1244.0, 213.0], [1223.0, 238.0], [1220.0, 282.0], [1205.0, 288.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.8b60a8acbaab729312e007c7c316e674.jpg</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>2</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Cap1</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>761</v>
+      </c>
+      <c r="H69" t="n">
+        <v>112</v>
+      </c>
+      <c r="I69" t="n">
+        <v>922</v>
+      </c>
+      <c r="J69" t="n">
+        <v>316</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="L69" t="n">
+        <v>16</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>[[867.0, 134.0], [833.0, 129.0], [799.0, 141.0], [769.0, 188.0], [769.0, 217.0], [753.0, 246.0], [760.0, 261.0], [790.0, 284.0], [818.0, 289.0], [825.0, 284.0], [842.0, 283.0], [857.0, 264.0], [898.0, 226.0], [906.0, 197.0], [903.0, 174.0], [886.0, 147.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.8b60a8acbaab729312e007c7c316e674.jpg</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>3</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Cap2</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>658</v>
+      </c>
+      <c r="H70" t="n">
+        <v>152</v>
+      </c>
+      <c r="I70" t="n">
+        <v>775</v>
+      </c>
+      <c r="J70" t="n">
+        <v>300</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="L70" t="n">
+        <v>19</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>[[740.0, 168.0], [732.0, 166.0], [711.0, 168.0], [695.0, 180.0], [686.0, 200.0], [661.0, 230.0], [660.0, 259.0], [666.0, 269.0], [693.0, 282.0], [703.0, 284.0], [712.0, 282.0], [726.0, 268.0], [735.0, 252.0], [746.0, 241.0], [753.0, 240.0], [764.0, 228.0], [767.0, 220.0], [766.0, 192.0], [752.0, 175.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.8b60a8acbaab729312e007c7c316e674.jpg</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>4</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Transformer_SMD</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Transformer_SMD:Transformer_Wuerth_WE-PoE_EP13</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>874</v>
+      </c>
+      <c r="H71" t="n">
+        <v>135</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1079</v>
+      </c>
+      <c r="J71" t="n">
+        <v>442</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="L71" t="n">
+        <v>28</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>[[1041.0, 167.0], [997.0, 159.0], [969.0, 189.0], [937.0, 189.0], [932.0, 215.0], [913.0, 218.0], [925.0, 224.0], [925.0, 241.0], [919.0, 228.0], [896.0, 233.0], [912.0, 253.0], [901.0, 257.0], [891.0, 296.0], [878.0, 308.0], [884.0, 339.0], [874.0, 348.0], [881.0, 367.0], [869.0, 373.0], [869.0, 381.0], [882.0, 397.0], [940.0, 413.0], [975.0, 408.0], [1025.0, 361.0], [1031.0, 340.0], [1066.0, 347.0], [1076.0, 341.0], [1086.0, 225.0], [1043.0, 213.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.8b60a8acbaab729312e007c7c316e674.jpg</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>5</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Cap3</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>1217</v>
+      </c>
+      <c r="H72" t="n">
+        <v>298</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1448</v>
+      </c>
+      <c r="J72" t="n">
+        <v>500</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="L72" t="n">
+        <v>16</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>[[1420.0, 362.0], [1406.0, 345.0], [1385.0, 331.0], [1354.0, 331.0], [1227.0, 396.0], [1219.0, 419.0], [1224.0, 446.0], [1240.0, 469.0], [1263.0, 480.0], [1310.0, 468.0], [1334.0, 452.0], [1356.0, 444.0], [1404.0, 438.0], [1418.0, 425.0], [1426.0, 409.0], [1428.0, 388.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.8b60a8acbaab729312e007c7c316e674.jpg</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>6</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Resistor_SMD</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>1248</v>
+      </c>
+      <c r="H73" t="n">
+        <v>59</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1346</v>
+      </c>
+      <c r="J73" t="n">
+        <v>132</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="L73" t="n">
+        <v>14</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>[[1319.0, 72.0], [1312.0, 68.0], [1304.0, 66.0], [1290.0, 67.0], [1279.0, 77.0], [1251.0, 110.0], [1254.0, 112.0], [1267.0, 113.0], [1276.0, 117.0], [1296.0, 122.0], [1303.0, 121.0], [1309.0, 111.0], [1318.0, 104.0], [1323.0, 96.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.8b60a8acbaab729312e007c7c316e674.jpg</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>7</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>MOSFET</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD:SOT-23</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>1076</v>
+      </c>
+      <c r="H74" t="n">
+        <v>347</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1204</v>
+      </c>
+      <c r="J74" t="n">
+        <v>491</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="L74" t="n">
+        <v>19</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>[[1119.0, 354.0], [1113.0, 359.0], [1113.0, 394.0], [1105.0, 401.0], [1106.0, 430.0], [1101.0, 437.0], [1103.0, 454.0], [1109.0, 462.0], [1133.0, 460.0], [1139.0, 463.0], [1147.0, 461.0], [1153.0, 465.0], [1170.0, 466.0], [1175.0, 461.0], [1178.0, 445.0], [1182.0, 370.0], [1180.0, 367.0], [1163.0, 364.0], [1152.0, 358.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.8b60a8acbaab729312e007c7c316e674.jpg</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>8</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Cap4</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>1204</v>
+      </c>
+      <c r="H75" t="n">
+        <v>423</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1442</v>
+      </c>
+      <c r="J75" t="n">
+        <v>624</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="L75" t="n">
+        <v>23</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>[[1419.0, 497.0], [1409.0, 474.0], [1382.0, 451.0], [1360.0, 447.0], [1337.0, 455.0], [1314.0, 473.0], [1261.0, 487.0], [1239.0, 498.0], [1233.0, 511.0], [1219.0, 513.0], [1198.0, 543.0], [1183.0, 552.0], [1183.0, 560.0], [1190.0, 562.0], [1197.0, 552.0], [1202.0, 569.0], [1219.0, 567.0], [1231.0, 583.0], [1257.0, 594.0], [1283.0, 592.0], [1384.0, 567.0], [1412.0, 548.0], [1421.0, 523.0]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>VID20210601144029-84_jpg.rf.8b60a8acbaab729312e007c7c316e674.jpg</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>9</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Mov</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Diode_SMD</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Diode_SMD:D_SOD-123</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>1058</v>
+      </c>
+      <c r="H76" t="n">
+        <v>25</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1196</v>
+      </c>
+      <c r="J76" t="n">
+        <v>232</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="L76" t="n">
+        <v>14</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>[[1109.0, 29.0], [1100.0, 37.0], [1095.0, 67.0], [1095.0, 140.0], [1090.0, 181.0], [1094.0, 225.0], [1139.0, 240.0], [1152.0, 231.0], [1158.0, 218.0], [1165.0, 147.0], [1154.0, 104.0], [1143.0, 82.0], [1140.0, 40.0], [1131.0, 33.0]]</t>
         </is>
       </c>
     </row>
